--- a/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2156" uniqueCount="463">
   <si>
     <t>Property</t>
   </si>
@@ -565,13 +565,7 @@
 ・Seriesの階層の(0008,0060)を集約する、または(0008,0060)　と　(0008, 0061) のOR。但し、重複する値は1つにまとめて表現。</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>「インスタンスにおける取得データの種類。」</t>
-  </si>
-  <si>
-    <t>http://dicom.nema.org/medical/dicom/current/output/chtml/part16/sect_CID_29.html</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
   </si>
   <si>
     <t>.code</t>
@@ -873,6 +867,9 @@
   <si>
     <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
 エラーコードなどを記載</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>コードは http://playbook.radlex.org/playbook/SearchRadlexAction に該当があれば使わなければならない。ただし、実施された行為のタイプにこれらのコードがなじまない場合は他のコードが利用される可能性がある。</t>
@@ -3343,13 +3340,11 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Y13" s="2"/>
+      <c r="Z13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3385,13 +3380,13 @@
         <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3399,10 +3394,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3425,16 +3420,16 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3484,7 +3479,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>90</v>
@@ -3499,16 +3494,16 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3516,10 +3511,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3542,16 +3537,16 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3601,7 +3596,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3616,16 +3611,16 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>79</v>
@@ -3633,14 +3628,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3659,16 +3654,16 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3682,7 +3677,7 @@
         <v>79</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>79</v>
@@ -3718,7 +3713,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3733,16 +3728,16 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>79</v>
@@ -3750,10 +3745,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3776,19 +3771,19 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3837,7 +3832,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3852,16 +3847,16 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3869,14 +3864,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3895,16 +3890,16 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3954,7 +3949,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3972,13 +3967,13 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -3986,14 +3981,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4012,16 +4007,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4071,7 +4066,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4089,13 +4084,13 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4103,10 +4098,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4129,19 +4124,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4190,7 +4185,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4208,7 +4203,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4222,14 +4217,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4248,16 +4243,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4307,7 +4302,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4325,10 +4320,10 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>79</v>
@@ -4339,14 +4334,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4365,16 +4360,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4424,7 +4419,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4442,10 +4437,10 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>79</v>
@@ -4456,10 +4451,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4482,16 +4477,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4541,7 +4536,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4556,13 +4551,13 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>79</v>
@@ -4573,14 +4568,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4599,16 +4594,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4634,14 +4629,14 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>175</v>
+        <v>267</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="Z24" t="s" s="2">
-        <v>270</v>
-      </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4658,7 +4653,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4673,13 +4668,13 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -4690,10 +4685,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4716,19 +4711,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4777,7 +4772,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4792,27 +4787,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>282</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4835,16 +4830,16 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4870,14 +4865,14 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="Y26" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Y26" t="s" s="2">
+      <c r="Z26" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4894,7 +4889,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4909,16 +4904,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4926,10 +4921,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4952,16 +4947,16 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5011,7 +5006,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5026,27 +5021,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>301</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5069,16 +5064,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5128,7 +5123,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5143,10 +5138,10 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -5160,14 +5155,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5186,16 +5181,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5245,7 +5240,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5263,10 +5258,10 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>79</v>
@@ -5277,10 +5272,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5303,16 +5298,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5362,7 +5357,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5380,7 +5375,7 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5394,10 +5389,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5420,13 +5415,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5477,7 +5472,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5495,7 +5490,7 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5509,10 +5504,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5541,7 +5536,7 @@
         <v>137</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>139</v>
@@ -5594,7 +5589,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5612,7 +5607,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5626,14 +5621,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5655,10 +5650,10 @@
         <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>139</v>
@@ -5713,7 +5708,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5745,14 +5740,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5774,16 +5769,16 @@
         <v>92</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5796,7 +5791,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5832,7 +5827,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>90</v>
@@ -5850,10 +5845,10 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
@@ -5864,14 +5859,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5890,16 +5885,16 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5913,7 +5908,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -5949,7 +5944,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5967,10 +5962,10 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5981,14 +5976,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6010,13 +6005,13 @@
         <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6042,14 +6037,12 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Y36" s="2"/>
+      <c r="Z36" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Y36" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>177</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6066,7 +6059,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>90</v>
@@ -6084,10 +6077,10 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -6098,14 +6091,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6124,16 +6117,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6147,7 +6140,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6183,7 +6176,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6201,10 +6194,10 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6215,14 +6208,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6241,16 +6234,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6300,7 +6293,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6318,10 +6311,10 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6332,10 +6325,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6358,19 +6351,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6419,7 +6412,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6437,7 +6430,7 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6451,14 +6444,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6480,13 +6473,13 @@
         <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6512,14 +6505,14 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>380</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6536,7 +6529,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6554,10 +6547,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6568,10 +6561,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6597,13 +6590,13 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6629,14 +6622,14 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6653,7 +6646,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6671,10 +6664,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6685,10 +6678,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6711,16 +6704,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6770,7 +6763,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6788,10 +6781,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6802,10 +6795,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6828,16 +6821,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6887,7 +6880,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6905,10 +6898,10 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6919,14 +6912,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6945,19 +6938,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7006,7 +6999,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7021,13 +7014,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -7038,10 +7031,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7064,13 +7057,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7121,7 +7114,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7139,7 +7132,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7153,10 +7146,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7185,7 +7178,7 @@
         <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7238,7 +7231,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7256,7 +7249,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7270,14 +7263,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7299,10 +7292,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -7357,7 +7350,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7389,10 +7382,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7415,17 +7408,17 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7450,14 +7443,14 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>175</v>
+        <v>267</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7474,7 +7467,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7492,7 +7485,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7506,10 +7499,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7532,16 +7525,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7591,7 +7584,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7609,24 +7602,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>426</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7649,16 +7642,16 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7708,7 +7701,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7726,7 +7719,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7740,10 +7733,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7766,13 +7759,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7823,7 +7816,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7841,7 +7834,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7855,10 +7848,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7887,7 +7880,7 @@
         <v>137</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>139</v>
@@ -7940,7 +7933,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7958,7 +7951,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7972,14 +7965,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8001,10 +7994,10 @@
         <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>139</v>
@@ -8059,7 +8052,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8091,14 +8084,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8120,16 +8113,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8142,7 +8135,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8178,7 +8171,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8196,10 +8189,10 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8210,14 +8203,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8239,13 +8232,13 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8271,14 +8264,14 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>175</v>
+        <v>267</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8295,7 +8288,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8313,10 +8306,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8327,14 +8320,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8353,16 +8346,16 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8412,7 +8405,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8430,10 +8423,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8444,10 +8437,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8470,16 +8463,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8529,7 +8522,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8547,10 +8540,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2156" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -1230,10 +1230,7 @@
     <t>コードは、列挙型またはコードリストで、どの部位の検査なのかを示す。フリーではなく、DICOM定義書の中で示される語句（コード）をデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
   </si>
   <si>
-    <t>DICOM tagに設定されているコードをデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -6507,11 +6504,9 @@
       <c r="X40" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="Y40" t="s" s="2">
+      <c r="Y40" s="2"/>
+      <c r="Z40" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6547,10 +6542,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6561,10 +6556,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6590,13 +6585,13 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6625,11 +6620,11 @@
         <v>286</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>387</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6646,7 +6641,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6664,10 +6659,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6678,10 +6673,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6704,16 +6699,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6763,7 +6758,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6781,10 +6776,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6795,10 +6790,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6824,13 +6819,13 @@
         <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6880,7 +6875,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6901,7 +6896,7 @@
         <v>204</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6912,14 +6907,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6941,16 +6936,16 @@
         <v>317</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6999,7 +6994,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7014,13 +7009,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>228</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -7031,10 +7026,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7146,10 +7141,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7263,10 +7258,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7382,10 +7377,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7411,14 +7406,14 @@
         <v>263</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7446,11 +7441,11 @@
         <v>267</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>417</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7467,7 +7462,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7499,10 +7494,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7525,16 +7520,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7584,7 +7579,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7602,24 +7597,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>425</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7645,13 +7640,13 @@
         <v>317</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7701,7 +7696,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7719,7 +7714,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7733,10 +7728,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7848,10 +7843,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7965,10 +7960,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8084,14 +8079,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8113,16 +8108,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8135,7 +8130,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8171,7 +8166,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8192,7 +8187,7 @@
         <v>341</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8203,14 +8198,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8232,13 +8227,13 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8267,11 +8262,11 @@
         <v>267</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8288,7 +8283,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8306,10 +8301,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8320,14 +8315,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8349,13 +8344,13 @@
         <v>240</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8405,7 +8400,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8423,10 +8418,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8437,10 +8432,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8466,13 +8461,13 @@
         <v>310</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8522,7 +8517,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8540,10 +8535,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
